--- a/partner_results/obi/ClassesWithMultipleEnglishLabels_obi.xlsx
+++ b/partner_results/obi/ClassesWithMultipleEnglishLabels_obi.xlsx
@@ -446,7 +446,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>assay | assay [obi]</t>
+          <t>validation | validation [obi]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -454,14 +454,10 @@
           <t>completely executed planned process</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>PlanAndPlannedProcess Branch</t>
-        </is>
-      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>A planned process that has the objective to produce information about a material entity (the evaluant) by examining it.</t>
+          <t>a planned process with objective to check that the accuracy or the quality of a claim or prediction  satisfies some criteria and which is assessed by comparing with independent results</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -469,7 +465,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>validation | validation [obi]</t>
+          <t>assay [obi] | assay</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -477,10 +473,14 @@
           <t>completely executed planned process</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>PlanAndPlannedProcess Branch</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>a planned process with objective to check that the accuracy or the quality of a claim or prediction satisfies some criteria and which is assessed by comparing with independent results</t>
+          <t>A planned process with the objective to produce information about the material entity that is the evaluant, by physically examining it or its proxies.</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
